--- a/data/nzd0001/nzd0001.xlsx
+++ b/data/nzd0001/nzd0001.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI207"/>
+  <dimension ref="A1:AI208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23436,6 +23436,117 @@
         </is>
       </c>
     </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>353.12</v>
+      </c>
+      <c r="C208" t="n">
+        <v>352.91</v>
+      </c>
+      <c r="D208" t="n">
+        <v>353.02</v>
+      </c>
+      <c r="E208" t="n">
+        <v>356.12</v>
+      </c>
+      <c r="F208" t="n">
+        <v>360.24</v>
+      </c>
+      <c r="G208" t="n">
+        <v>371.11</v>
+      </c>
+      <c r="H208" t="n">
+        <v>382.32</v>
+      </c>
+      <c r="I208" t="n">
+        <v>396.31</v>
+      </c>
+      <c r="J208" t="n">
+        <v>379.56</v>
+      </c>
+      <c r="K208" t="n">
+        <v>373.13</v>
+      </c>
+      <c r="L208" t="n">
+        <v>361.11</v>
+      </c>
+      <c r="M208" t="n">
+        <v>354.67</v>
+      </c>
+      <c r="N208" t="n">
+        <v>349</v>
+      </c>
+      <c r="O208" t="n">
+        <v>346.3</v>
+      </c>
+      <c r="P208" t="n">
+        <v>344.2</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>338.63</v>
+      </c>
+      <c r="R208" t="n">
+        <v>335.26</v>
+      </c>
+      <c r="S208" t="n">
+        <v>332.82</v>
+      </c>
+      <c r="T208" t="n">
+        <v>333.34</v>
+      </c>
+      <c r="U208" t="n">
+        <v>334.99</v>
+      </c>
+      <c r="V208" t="n">
+        <v>338.89</v>
+      </c>
+      <c r="W208" t="n">
+        <v>344.71</v>
+      </c>
+      <c r="X208" t="n">
+        <v>344.39</v>
+      </c>
+      <c r="Y208" t="n">
+        <v>338.19</v>
+      </c>
+      <c r="Z208" t="n">
+        <v>333.78</v>
+      </c>
+      <c r="AA208" t="n">
+        <v>334.76</v>
+      </c>
+      <c r="AB208" t="n">
+        <v>335.75</v>
+      </c>
+      <c r="AC208" t="n">
+        <v>334.69</v>
+      </c>
+      <c r="AD208" t="n">
+        <v>339.34</v>
+      </c>
+      <c r="AE208" t="n">
+        <v>336.02</v>
+      </c>
+      <c r="AF208" t="n">
+        <v>334.84</v>
+      </c>
+      <c r="AG208" t="n">
+        <v>335.07</v>
+      </c>
+      <c r="AH208" t="n">
+        <v>339.71</v>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23447,7 +23558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B207"/>
+  <dimension ref="A1:B208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25520,6 +25631,16 @@
       </c>
       <c r="B207" t="n">
         <v>0.77</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>-0.95</v>
       </c>
     </row>
   </sheetData>
@@ -25688,28 +25809,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1448704583130645</v>
+        <v>-0.1179228339945427</v>
       </c>
       <c r="J2" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K2" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002974105593638532</v>
+        <v>0.001969957839300762</v>
       </c>
       <c r="M2" t="n">
-        <v>17.16068518017042</v>
+        <v>17.20104077644033</v>
       </c>
       <c r="N2" t="n">
-        <v>440.8404732764321</v>
+        <v>443.4484493645871</v>
       </c>
       <c r="O2" t="n">
-        <v>20.99620140112092</v>
+        <v>21.05821572129479</v>
       </c>
       <c r="P2" t="n">
-        <v>325.6382420228051</v>
+        <v>325.3637407826855</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25766,28 +25887,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08396751976793709</v>
+        <v>-0.06064687969343515</v>
       </c>
       <c r="J3" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K3" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001291371789082341</v>
+        <v>0.0006733839119388296</v>
       </c>
       <c r="M3" t="n">
-        <v>14.98966394866506</v>
+        <v>15.01165526156519</v>
       </c>
       <c r="N3" t="n">
-        <v>346.0117225572453</v>
+        <v>347.956099435581</v>
       </c>
       <c r="O3" t="n">
-        <v>18.60139033936026</v>
+        <v>18.65358141043111</v>
       </c>
       <c r="P3" t="n">
-        <v>327.71975785513</v>
+        <v>327.4847264051272</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25844,28 +25965,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2081645015479678</v>
+        <v>-0.1871058980011508</v>
       </c>
       <c r="J4" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K4" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009856524288122892</v>
+        <v>0.007968270723046733</v>
       </c>
       <c r="M4" t="n">
-        <v>13.90644108913249</v>
+        <v>13.91528774474252</v>
       </c>
       <c r="N4" t="n">
-        <v>276.228401684972</v>
+        <v>277.8428662554693</v>
       </c>
       <c r="O4" t="n">
-        <v>16.62012038719852</v>
+        <v>16.66861920662504</v>
       </c>
       <c r="P4" t="n">
-        <v>333.8366855810612</v>
+        <v>333.6244515209825</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25922,28 +26043,28 @@
         <v>0.0759</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2465949171093907</v>
+        <v>-0.2300639079107836</v>
       </c>
       <c r="J5" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K5" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01801712756467178</v>
+        <v>0.01572972349168189</v>
       </c>
       <c r="M5" t="n">
-        <v>12.17329867725501</v>
+        <v>12.17127533840048</v>
       </c>
       <c r="N5" t="n">
-        <v>213.3151461879974</v>
+        <v>214.1395330425548</v>
       </c>
       <c r="O5" t="n">
-        <v>14.60531225917465</v>
+        <v>14.63350720239529</v>
       </c>
       <c r="P5" t="n">
-        <v>343.0542172748035</v>
+        <v>342.8895781509015</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26000,28 +26121,28 @@
         <v>0.0788</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3445300761566585</v>
+        <v>-0.33303909017381</v>
       </c>
       <c r="J6" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K6" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03891635621805611</v>
+        <v>0.03662018080083096</v>
       </c>
       <c r="M6" t="n">
-        <v>11.20263937331507</v>
+        <v>11.18766422698198</v>
       </c>
       <c r="N6" t="n">
-        <v>188.6767509635913</v>
+        <v>188.6574967332944</v>
       </c>
       <c r="O6" t="n">
-        <v>13.73596559997117</v>
+        <v>13.73526471289485</v>
       </c>
       <c r="P6" t="n">
-        <v>355.8208477313158</v>
+        <v>355.7064042728277</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26078,28 +26199,28 @@
         <v>0.0849</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3001893890606628</v>
+        <v>-0.2914192940854912</v>
       </c>
       <c r="J7" t="n">
+        <v>207</v>
+      </c>
+      <c r="K7" t="n">
         <v>206</v>
       </c>
-      <c r="K7" t="n">
-        <v>205</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.03629951052044567</v>
+        <v>0.03447775196203984</v>
       </c>
       <c r="M7" t="n">
-        <v>9.988411405219619</v>
+        <v>9.968220662651987</v>
       </c>
       <c r="N7" t="n">
-        <v>153.56553190039</v>
+        <v>153.3471349951478</v>
       </c>
       <c r="O7" t="n">
-        <v>12.3921560634294</v>
+        <v>12.38334102716822</v>
       </c>
       <c r="P7" t="n">
-        <v>368.6930408979378</v>
+        <v>368.6054480769217</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26156,28 +26277,28 @@
         <v>0.0912</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3195481766969322</v>
+        <v>-0.3156285752512841</v>
       </c>
       <c r="J8" t="n">
+        <v>207</v>
+      </c>
+      <c r="K8" t="n">
         <v>206</v>
       </c>
-      <c r="K8" t="n">
-        <v>205</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.04979199739098006</v>
+        <v>0.04903277842138409</v>
       </c>
       <c r="M8" t="n">
-        <v>8.948973764969239</v>
+        <v>8.919580779026893</v>
       </c>
       <c r="N8" t="n">
-        <v>125.0816457814898</v>
+        <v>124.5797321248966</v>
       </c>
       <c r="O8" t="n">
-        <v>11.18399060181516</v>
+        <v>11.16152911230789</v>
       </c>
       <c r="P8" t="n">
-        <v>386.2259699210007</v>
+        <v>386.1868222323092</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26234,28 +26355,28 @@
         <v>0.0881</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2143027356213223</v>
+        <v>-0.2084506963652588</v>
       </c>
       <c r="J9" t="n">
+        <v>207</v>
+      </c>
+      <c r="K9" t="n">
         <v>206</v>
       </c>
-      <c r="K9" t="n">
-        <v>205</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.02548294600892065</v>
+        <v>0.02431536079588426</v>
       </c>
       <c r="M9" t="n">
-        <v>8.741109589275839</v>
+        <v>8.723291387531239</v>
       </c>
       <c r="N9" t="n">
-        <v>112.734541572906</v>
+        <v>112.4219640765065</v>
       </c>
       <c r="O9" t="n">
-        <v>10.61765235694341</v>
+        <v>10.60292243093886</v>
       </c>
       <c r="P9" t="n">
-        <v>395.0730849146409</v>
+        <v>395.0146366733634</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26312,28 +26433,28 @@
         <v>0.0973</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1982670334192592</v>
+        <v>-0.1982650310739172</v>
       </c>
       <c r="J10" t="n">
+        <v>207</v>
+      </c>
+      <c r="K10" t="n">
         <v>206</v>
       </c>
-      <c r="K10" t="n">
-        <v>205</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.02557268723542061</v>
+        <v>0.0258065914745943</v>
       </c>
       <c r="M10" t="n">
-        <v>7.68438361228389</v>
+        <v>7.647090383378406</v>
       </c>
       <c r="N10" t="n">
-        <v>96.14702752060745</v>
+        <v>95.68029440477841</v>
       </c>
       <c r="O10" t="n">
-        <v>9.805459067305694</v>
+        <v>9.781630457381755</v>
       </c>
       <c r="P10" t="n">
-        <v>384.8874650690756</v>
+        <v>384.8874450703096</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26390,28 +26511,28 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2435629725249547</v>
+        <v>-0.2418073673999131</v>
       </c>
       <c r="J11" t="n">
+        <v>207</v>
+      </c>
+      <c r="K11" t="n">
         <v>206</v>
       </c>
-      <c r="K11" t="n">
-        <v>205</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.04400181486353671</v>
+        <v>0.04377691823169472</v>
       </c>
       <c r="M11" t="n">
-        <v>6.9419751544341</v>
+        <v>6.919604356855348</v>
       </c>
       <c r="N11" t="n">
-        <v>82.73147617078448</v>
+        <v>82.35098788349069</v>
       </c>
       <c r="O11" t="n">
-        <v>9.095684480608618</v>
+        <v>9.074744507890605</v>
       </c>
       <c r="P11" t="n">
-        <v>377.5769197301047</v>
+        <v>377.5593853241573</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26468,28 +26589,28 @@
         <v>0.0901</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2530906997039001</v>
+        <v>-0.2553646893841985</v>
       </c>
       <c r="J12" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K12" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04943292356827667</v>
+        <v>0.05070594421608665</v>
       </c>
       <c r="M12" t="n">
-        <v>6.853211039948966</v>
+        <v>6.832099583198041</v>
       </c>
       <c r="N12" t="n">
-        <v>80.02723453305023</v>
+        <v>79.67663577718194</v>
       </c>
       <c r="O12" t="n">
-        <v>8.94579423712899</v>
+        <v>8.926176996742891</v>
       </c>
       <c r="P12" t="n">
-        <v>370.6653478218678</v>
+        <v>370.6878203985112</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26546,28 +26667,28 @@
         <v>0.0857</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2515687553060432</v>
+        <v>-0.2543654891057436</v>
       </c>
       <c r="J13" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K13" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05224900012992717</v>
+        <v>0.05379066974025648</v>
       </c>
       <c r="M13" t="n">
-        <v>6.802467324403489</v>
+        <v>6.784050902001455</v>
       </c>
       <c r="N13" t="n">
-        <v>74.58450882087459</v>
+        <v>74.27866037439769</v>
       </c>
       <c r="O13" t="n">
-        <v>8.636232327865814</v>
+        <v>8.618506852952992</v>
       </c>
       <c r="P13" t="n">
-        <v>364.8207492812055</v>
+        <v>364.8483878475586</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26624,28 +26745,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1557249892787198</v>
+        <v>-0.1610573307297424</v>
       </c>
       <c r="J14" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K14" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02526569063234962</v>
+        <v>0.02713770424068596</v>
       </c>
       <c r="M14" t="n">
-        <v>6.313349793013277</v>
+        <v>6.315826364334929</v>
       </c>
       <c r="N14" t="n">
-        <v>60.78419406790482</v>
+        <v>60.68853763794152</v>
       </c>
       <c r="O14" t="n">
-        <v>7.796421875957254</v>
+        <v>7.790284823929195</v>
       </c>
       <c r="P14" t="n">
-        <v>359.6320744876818</v>
+        <v>359.6847710557382</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -26702,28 +26823,28 @@
         <v>0.0984</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1684100125632116</v>
+        <v>-0.1747587161562813</v>
       </c>
       <c r="J15" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K15" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02821188343572478</v>
+        <v>0.03045758361927131</v>
       </c>
       <c r="M15" t="n">
-        <v>6.623094660635346</v>
+        <v>6.627259571329374</v>
       </c>
       <c r="N15" t="n">
-        <v>63.47376862334487</v>
+        <v>63.44778585438281</v>
       </c>
       <c r="O15" t="n">
-        <v>7.967042652286033</v>
+        <v>7.965411844618131</v>
       </c>
       <c r="P15" t="n">
-        <v>358.5071445390724</v>
+        <v>358.5698852495152</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -26780,28 +26901,28 @@
         <v>0.1072</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.154364082850253</v>
+        <v>-0.1625049989484188</v>
       </c>
       <c r="J16" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K16" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02703533249542445</v>
+        <v>0.02990486582203111</v>
       </c>
       <c r="M16" t="n">
-        <v>6.276182922340408</v>
+        <v>6.288856782456915</v>
       </c>
       <c r="N16" t="n">
-        <v>55.7156026995217</v>
+        <v>55.90791934303067</v>
       </c>
       <c r="O16" t="n">
-        <v>7.464288492516999</v>
+        <v>7.477159844689069</v>
       </c>
       <c r="P16" t="n">
-        <v>358.1963238098501</v>
+        <v>358.2767759607762</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -26858,28 +26979,28 @@
         <v>0.0876</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1804025010012048</v>
+        <v>-0.1884758604928046</v>
       </c>
       <c r="J17" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K17" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03585335824025349</v>
+        <v>0.0390564911638811</v>
       </c>
       <c r="M17" t="n">
-        <v>6.237881522956222</v>
+        <v>6.25517030548418</v>
       </c>
       <c r="N17" t="n">
-        <v>56.86137077556375</v>
+        <v>57.04052508901663</v>
       </c>
       <c r="O17" t="n">
-        <v>7.540647901577407</v>
+        <v>7.552517797994033</v>
       </c>
       <c r="P17" t="n">
-        <v>353.2474871025794</v>
+        <v>353.3272716290955</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -26936,28 +27057,28 @@
         <v>0.0929</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1025757571327834</v>
+        <v>-0.1111064414941298</v>
       </c>
       <c r="J18" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K18" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01262528226964121</v>
+        <v>0.01477804836126129</v>
       </c>
       <c r="M18" t="n">
-        <v>6.015009851569139</v>
+        <v>6.03250348414801</v>
       </c>
       <c r="N18" t="n">
-        <v>53.46250861452201</v>
+        <v>53.71095622809975</v>
       </c>
       <c r="O18" t="n">
-        <v>7.311806111660922</v>
+        <v>7.328775902434168</v>
       </c>
       <c r="P18" t="n">
-        <v>348.3309111143565</v>
+        <v>348.4152151284831</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -27014,28 +27135,28 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.03144221749117779</v>
+        <v>-0.04037311570948102</v>
       </c>
       <c r="J19" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K19" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0009393259209909965</v>
+        <v>0.00154962752010035</v>
       </c>
       <c r="M19" t="n">
-        <v>6.704145513780169</v>
+        <v>6.710370311640945</v>
       </c>
       <c r="N19" t="n">
-        <v>68.31575255569615</v>
+        <v>68.54110586451422</v>
       </c>
       <c r="O19" t="n">
-        <v>8.265334388619504</v>
+        <v>8.278955602279446</v>
       </c>
       <c r="P19" t="n">
-        <v>344.4690568336025</v>
+        <v>344.5573159389293</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -27092,28 +27213,28 @@
         <v>0.0948</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.06426787317747293</v>
+        <v>-0.07315122723952716</v>
       </c>
       <c r="J20" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K20" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L20" t="n">
-        <v>0.002902265254313474</v>
+        <v>0.003769406607104231</v>
       </c>
       <c r="M20" t="n">
-        <v>7.632216027136323</v>
+        <v>7.630593279026987</v>
       </c>
       <c r="N20" t="n">
-        <v>92.19501679059279</v>
+        <v>92.29911386745962</v>
       </c>
       <c r="O20" t="n">
-        <v>9.601823617969286</v>
+        <v>9.60724278174855</v>
       </c>
       <c r="P20" t="n">
-        <v>345.8132211456563</v>
+        <v>345.9010103985012</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -27170,28 +27291,28 @@
         <v>0.0984</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.05804667797704295</v>
+        <v>-0.06802847411382787</v>
       </c>
       <c r="J21" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K21" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L21" t="n">
-        <v>0.002434954458892746</v>
+        <v>0.003346642028005054</v>
       </c>
       <c r="M21" t="n">
-        <v>7.376015032744859</v>
+        <v>7.377596248504291</v>
       </c>
       <c r="N21" t="n">
-        <v>89.68588228742476</v>
+        <v>89.94639145457811</v>
       </c>
       <c r="O21" t="n">
-        <v>9.470263052704754</v>
+        <v>9.484007141212944</v>
       </c>
       <c r="P21" t="n">
-        <v>348.6177703371135</v>
+        <v>348.7164148827184</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -27248,28 +27369,28 @@
         <v>0.1042</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1140779860782788</v>
+        <v>-0.1244257710421866</v>
       </c>
       <c r="J22" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K22" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L22" t="n">
-        <v>0.007688806185107033</v>
+        <v>0.00915615715539686</v>
       </c>
       <c r="M22" t="n">
-        <v>7.649224284582424</v>
+        <v>7.657479774683116</v>
       </c>
       <c r="N22" t="n">
-        <v>109.1218280128538</v>
+        <v>109.3402517517406</v>
       </c>
       <c r="O22" t="n">
-        <v>10.44613938318141</v>
+        <v>10.45658891569046</v>
       </c>
       <c r="P22" t="n">
-        <v>354.4660924156079</v>
+        <v>354.5683538254578</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -27326,28 +27447,28 @@
         <v>0.09909999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1342037709179355</v>
+        <v>-0.1447323169652559</v>
       </c>
       <c r="J23" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K23" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L23" t="n">
-        <v>0.00971843085099322</v>
+        <v>0.01131701399310925</v>
       </c>
       <c r="M23" t="n">
-        <v>7.987222931642543</v>
+        <v>7.994071566592771</v>
       </c>
       <c r="N23" t="n">
-        <v>119.2369750900241</v>
+        <v>119.4328094247788</v>
       </c>
       <c r="O23" t="n">
-        <v>10.91956844797559</v>
+        <v>10.92853189704723</v>
       </c>
       <c r="P23" t="n">
-        <v>361.0547171107696</v>
+        <v>361.1587648819808</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -27404,28 +27525,28 @@
         <v>0.1154</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1337316777399679</v>
+        <v>-0.1431857476963302</v>
       </c>
       <c r="J24" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K24" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L24" t="n">
-        <v>0.008732412313878446</v>
+        <v>0.01004356113114979</v>
       </c>
       <c r="M24" t="n">
-        <v>8.665220326771715</v>
+        <v>8.669154833077314</v>
       </c>
       <c r="N24" t="n">
-        <v>131.8998262395906</v>
+        <v>131.8849843779539</v>
       </c>
       <c r="O24" t="n">
-        <v>11.4847649623138</v>
+        <v>11.48411878978766</v>
       </c>
       <c r="P24" t="n">
-        <v>359.4191182285437</v>
+        <v>359.5125475494978</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -27482,28 +27603,28 @@
         <v>0.1198</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.09239221464710314</v>
+        <v>-0.1032880278470045</v>
       </c>
       <c r="J25" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K25" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L25" t="n">
-        <v>0.004025531691745798</v>
+        <v>0.005042423374898575</v>
       </c>
       <c r="M25" t="n">
-        <v>8.855201920607307</v>
+        <v>8.861940442800433</v>
       </c>
       <c r="N25" t="n">
-        <v>137.2191341737625</v>
+        <v>137.3828868432141</v>
       </c>
       <c r="O25" t="n">
-        <v>11.71405711842667</v>
+        <v>11.72104461399299</v>
       </c>
       <c r="P25" t="n">
-        <v>353.850439915461</v>
+        <v>353.9581171838976</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -27560,28 +27681,28 @@
         <v>0.1172</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.01473563453929834</v>
+        <v>-0.02594537306786901</v>
       </c>
       <c r="J26" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K26" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L26" t="n">
-        <v>7.292063984210007e-05</v>
+        <v>0.0002271160815064954</v>
       </c>
       <c r="M26" t="n">
-        <v>10.22532694860607</v>
+        <v>10.22469359048543</v>
       </c>
       <c r="N26" t="n">
-        <v>193.4525718126137</v>
+        <v>193.3929855417795</v>
       </c>
       <c r="O26" t="n">
-        <v>13.90872286777667</v>
+        <v>13.90658065599806</v>
       </c>
       <c r="P26" t="n">
-        <v>347.7338060939741</v>
+        <v>347.8445857120255</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -27638,28 +27759,28 @@
         <v>0.1254</v>
       </c>
       <c r="I27" t="n">
-        <v>0.138244493431023</v>
+        <v>0.1278075302602791</v>
       </c>
       <c r="J27" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K27" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L27" t="n">
-        <v>0.005212900546800014</v>
+        <v>0.004486118201303957</v>
       </c>
       <c r="M27" t="n">
-        <v>11.37455704662717</v>
+        <v>11.36546796113383</v>
       </c>
       <c r="N27" t="n">
-        <v>236.9547138855673</v>
+        <v>236.5684938272776</v>
       </c>
       <c r="O27" t="n">
-        <v>15.39333342345209</v>
+        <v>15.380783264427</v>
       </c>
       <c r="P27" t="n">
-        <v>343.6647895185309</v>
+        <v>343.7679322270538</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -27716,28 +27837,28 @@
         <v>0.1321</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2279766301585226</v>
+        <v>0.2169392279365538</v>
       </c>
       <c r="J28" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K28" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L28" t="n">
-        <v>0.0146845077650497</v>
+        <v>0.01338894596102547</v>
       </c>
       <c r="M28" t="n">
-        <v>11.56132681893883</v>
+        <v>11.55671974798087</v>
       </c>
       <c r="N28" t="n">
-        <v>226.57685401872</v>
+        <v>226.3305507163184</v>
       </c>
       <c r="O28" t="n">
-        <v>15.05247003048736</v>
+        <v>15.04428631462186</v>
       </c>
       <c r="P28" t="n">
-        <v>342.9610380303698</v>
+        <v>343.0701145444484</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -27794,28 +27915,28 @@
         <v>0.1514</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1940377364615344</v>
+        <v>0.1805902227436562</v>
       </c>
       <c r="J29" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K29" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L29" t="n">
-        <v>0.009613911154443211</v>
+        <v>0.008374057651145961</v>
       </c>
       <c r="M29" t="n">
-        <v>12.11570742533865</v>
+        <v>12.11368693676276</v>
       </c>
       <c r="N29" t="n">
-        <v>251.9972441439717</v>
+        <v>252.0390374275974</v>
       </c>
       <c r="O29" t="n">
-        <v>15.87442106484428</v>
+        <v>15.87573738216897</v>
       </c>
       <c r="P29" t="n">
-        <v>345.7267010036519</v>
+        <v>345.8595953106521</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -27872,28 +27993,28 @@
         <v>0.2</v>
       </c>
       <c r="I30" t="n">
-        <v>0.237013615929211</v>
+        <v>0.22314814702522</v>
       </c>
       <c r="J30" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K30" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L30" t="n">
-        <v>0.01415819787091221</v>
+        <v>0.0126207051809395</v>
       </c>
       <c r="M30" t="n">
-        <v>12.16646524715316</v>
+        <v>12.16226908169676</v>
       </c>
       <c r="N30" t="n">
-        <v>254.1351915611989</v>
+        <v>254.2461442473392</v>
       </c>
       <c r="O30" t="n">
-        <v>15.94161822279027</v>
+        <v>15.94509781241053</v>
       </c>
       <c r="P30" t="n">
-        <v>349.729894420569</v>
+        <v>349.8669191464689</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -27950,28 +28071,28 @@
         <v>0.182</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1977736986592419</v>
+        <v>0.1824456115201606</v>
       </c>
       <c r="J31" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K31" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L31" t="n">
-        <v>0.009697532902866346</v>
+        <v>0.008289290410943173</v>
       </c>
       <c r="M31" t="n">
-        <v>12.10063892944684</v>
+        <v>12.09857434385709</v>
       </c>
       <c r="N31" t="n">
-        <v>259.5151014586275</v>
+        <v>259.8973805960044</v>
       </c>
       <c r="O31" t="n">
-        <v>16.10947241403726</v>
+        <v>16.1213330899155</v>
       </c>
       <c r="P31" t="n">
-        <v>349.2387711801278</v>
+        <v>349.3902501494542</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -28028,28 +28149,28 @@
         <v>0.166</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1884127111488229</v>
+        <v>0.1727703021348048</v>
       </c>
       <c r="J32" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K32" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L32" t="n">
-        <v>0.008408743250834294</v>
+        <v>0.007101457312074011</v>
       </c>
       <c r="M32" t="n">
-        <v>12.43406714254506</v>
+        <v>12.43118072035067</v>
       </c>
       <c r="N32" t="n">
-        <v>271.982498523499</v>
+        <v>272.3723321263467</v>
       </c>
       <c r="O32" t="n">
-        <v>16.49189190249254</v>
+        <v>16.50370661779791</v>
       </c>
       <c r="P32" t="n">
-        <v>348.6830975470776</v>
+        <v>348.8376827848654</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -28106,28 +28227,28 @@
         <v>0.1505</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1805500577922408</v>
+        <v>0.1629841982414933</v>
       </c>
       <c r="J33" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K33" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L33" t="n">
-        <v>0.007750348143129471</v>
+        <v>0.006333503290417153</v>
       </c>
       <c r="M33" t="n">
-        <v>12.35728632981657</v>
+        <v>12.36461884607515</v>
       </c>
       <c r="N33" t="n">
-        <v>271.1527242440288</v>
+        <v>271.9913288241475</v>
       </c>
       <c r="O33" t="n">
-        <v>16.46671564836257</v>
+        <v>16.49215961674357</v>
       </c>
       <c r="P33" t="n">
-        <v>351.45147438663</v>
+        <v>351.6250680174552</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -28184,28 +28305,28 @@
         <v>0.1493</v>
       </c>
       <c r="I34" t="n">
-        <v>0.117484776077845</v>
+        <v>0.1006350523600416</v>
       </c>
       <c r="J34" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K34" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L34" t="n">
-        <v>0.00311930712174513</v>
+        <v>0.002296167880535549</v>
       </c>
       <c r="M34" t="n">
-        <v>13.06935409283163</v>
+        <v>13.06872792520254</v>
       </c>
       <c r="N34" t="n">
-        <v>286.5940697746922</v>
+        <v>287.1864650197851</v>
       </c>
       <c r="O34" t="n">
-        <v>16.92908945497933</v>
+        <v>16.94657679355288</v>
       </c>
       <c r="P34" t="n">
-        <v>356.9268377052452</v>
+        <v>357.0933541634991</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -28243,7 +28364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI207"/>
+  <dimension ref="A1:AI208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64809,6 +64930,183 @@
         </is>
       </c>
     </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>-34.42592412967132,172.96361064593975</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>-34.42591357175735,172.96450886961935</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>-34.42590012838619,172.96540703547456</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>-34.42585972404359,172.9663046605895</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>-34.42581012231705,172.96720210079343</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-34.42569965553859,172.96809831894348</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-34.425586601390606,172.96898283707424</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>-34.42537193897224,172.96977471546106</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>-34.425216325656535,172.97062115180995</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>-34.42496112865795,172.97146733075638</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>-34.42475177405073,172.97233881644297</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>-34.42449665617449,172.97318504186254</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>-34.42423522214606,172.97402778187123</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>-34.423949092241365,172.97485802931024</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>-34.42364791242461,172.97568976106572</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>-34.423319183142475,172.97650719407184</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>-34.4229766936806,172.97730459012516</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>-34.422626930614726,172.97809694355465</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>-34.42225402114,172.9788732468586</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>-34.42187227444916,172.97964342282623</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>-34.42147293321799,172.9804013982748</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>-34.42105317082498,172.98116030699228</t>
+        </is>
+      </c>
+      <c r="X208" t="inlineStr">
+        <is>
+          <t>-34.42060400271296,172.981895945636</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>-34.42016044427896,172.9826277512198</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>-34.419708369000126,172.98334106544866</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>-34.419219406444135,172.98401617563877</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>-34.41873037272468,172.98469121495987</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>-34.41825536451237,172.98538078454942</t>
+        </is>
+      </c>
+      <c r="AD208" t="inlineStr">
+        <is>
+          <t>-34.417733928579125,172.986040248144</t>
+        </is>
+      </c>
+      <c r="AE208" t="inlineStr">
+        <is>
+          <t>-34.417210612745,172.98669825506897</t>
+        </is>
+      </c>
+      <c r="AF208" t="inlineStr">
+        <is>
+          <t>-34.41667532891659,172.98732226074762</t>
+        </is>
+      </c>
+      <c r="AG208" t="inlineStr">
+        <is>
+          <t>-34.41613245437984,172.98793375711892</t>
+        </is>
+      </c>
+      <c r="AH208" t="inlineStr">
+        <is>
+          <t>-34.41556244449836,172.9885101657374</t>
+        </is>
+      </c>
+      <c r="AI208" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0001/nzd0001.xlsx
+++ b/data/nzd0001/nzd0001.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI208"/>
+  <dimension ref="A1:AI209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23547,6 +23547,117 @@
         </is>
       </c>
     </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>343.93</v>
+      </c>
+      <c r="C209" t="n">
+        <v>348.71</v>
+      </c>
+      <c r="D209" t="n">
+        <v>351.26</v>
+      </c>
+      <c r="E209" t="n">
+        <v>356.02</v>
+      </c>
+      <c r="F209" t="n">
+        <v>361.65</v>
+      </c>
+      <c r="G209" t="n">
+        <v>372.82</v>
+      </c>
+      <c r="H209" t="n">
+        <v>385.49</v>
+      </c>
+      <c r="I209" t="n">
+        <v>400.86</v>
+      </c>
+      <c r="J209" t="n">
+        <v>381.02</v>
+      </c>
+      <c r="K209" t="n">
+        <v>378.55</v>
+      </c>
+      <c r="L209" t="n">
+        <v>362.09</v>
+      </c>
+      <c r="M209" t="n">
+        <v>354.52</v>
+      </c>
+      <c r="N209" t="n">
+        <v>348.11</v>
+      </c>
+      <c r="O209" t="n">
+        <v>345.72</v>
+      </c>
+      <c r="P209" t="n">
+        <v>343.35</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>337.95</v>
+      </c>
+      <c r="R209" t="n">
+        <v>333.62</v>
+      </c>
+      <c r="S209" t="n">
+        <v>330.87</v>
+      </c>
+      <c r="T209" t="n">
+        <v>330.91</v>
+      </c>
+      <c r="U209" t="n">
+        <v>333</v>
+      </c>
+      <c r="V209" t="n">
+        <v>336.91</v>
+      </c>
+      <c r="W209" t="n">
+        <v>342.39</v>
+      </c>
+      <c r="X209" t="n">
+        <v>345.36</v>
+      </c>
+      <c r="Y209" t="n">
+        <v>337.5</v>
+      </c>
+      <c r="Z209" t="n">
+        <v>329.27</v>
+      </c>
+      <c r="AA209" t="n">
+        <v>331.1</v>
+      </c>
+      <c r="AB209" t="n">
+        <v>333.69</v>
+      </c>
+      <c r="AC209" t="n">
+        <v>332.45</v>
+      </c>
+      <c r="AD209" t="n">
+        <v>338.11</v>
+      </c>
+      <c r="AE209" t="n">
+        <v>333.79</v>
+      </c>
+      <c r="AF209" t="n">
+        <v>335.64</v>
+      </c>
+      <c r="AG209" t="n">
+        <v>336.29</v>
+      </c>
+      <c r="AH209" t="n">
+        <v>341.54</v>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23558,7 +23669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B208"/>
+  <dimension ref="A1:B209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25641,6 +25752,16 @@
       </c>
       <c r="B208" t="n">
         <v>-0.95</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -25809,28 +25930,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1179228339945427</v>
+        <v>-0.09913601822177415</v>
       </c>
       <c r="J2" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K2" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001969957839300762</v>
+        <v>0.001399406639783107</v>
       </c>
       <c r="M2" t="n">
-        <v>17.20104077644033</v>
+        <v>17.20133851709449</v>
       </c>
       <c r="N2" t="n">
-        <v>443.4484493645871</v>
+        <v>443.5623279236136</v>
       </c>
       <c r="O2" t="n">
-        <v>21.05821572129479</v>
+        <v>21.06091944630181</v>
       </c>
       <c r="P2" t="n">
-        <v>325.3637407826855</v>
+        <v>325.1702610429501</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25887,28 +26008,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.06064687969343515</v>
+        <v>-0.04111945652311735</v>
       </c>
       <c r="J3" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K3" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0006733839119388296</v>
+        <v>0.0003104240613763798</v>
       </c>
       <c r="M3" t="n">
-        <v>15.01165526156519</v>
+        <v>15.01668951423941</v>
       </c>
       <c r="N3" t="n">
-        <v>347.956099435581</v>
+        <v>348.7727831188155</v>
       </c>
       <c r="O3" t="n">
-        <v>18.65358141043111</v>
+        <v>18.67545938173451</v>
       </c>
       <c r="P3" t="n">
-        <v>327.4847264051272</v>
+        <v>327.2857339043593</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25965,28 +26086,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1871058980011508</v>
+        <v>-0.1677139963082994</v>
       </c>
       <c r="J4" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K4" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007968270723046733</v>
+        <v>0.00641694550554528</v>
       </c>
       <c r="M4" t="n">
-        <v>13.91528774474252</v>
+        <v>13.91645092424154</v>
       </c>
       <c r="N4" t="n">
-        <v>277.8428662554693</v>
+        <v>278.9667917548163</v>
       </c>
       <c r="O4" t="n">
-        <v>16.66861920662504</v>
+        <v>16.70229899609081</v>
       </c>
       <c r="P4" t="n">
-        <v>333.6244515209825</v>
+        <v>333.4268400399977</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26043,28 +26164,28 @@
         <v>0.0759</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2300639079107836</v>
+        <v>-0.213720878650095</v>
       </c>
       <c r="J5" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K5" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01572972349168189</v>
+        <v>0.01362010917785361</v>
       </c>
       <c r="M5" t="n">
-        <v>12.17127533840048</v>
+        <v>12.16702043525803</v>
       </c>
       <c r="N5" t="n">
-        <v>214.1395330425548</v>
+        <v>214.8955637686647</v>
       </c>
       <c r="O5" t="n">
-        <v>14.63350720239529</v>
+        <v>14.65931662011107</v>
       </c>
       <c r="P5" t="n">
-        <v>342.8895781509015</v>
+        <v>342.7249776481895</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26121,28 +26242,28 @@
         <v>0.0788</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.33303909017381</v>
+        <v>-0.3204049045058111</v>
       </c>
       <c r="J6" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K6" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03662018080083096</v>
+        <v>0.03411593884498187</v>
       </c>
       <c r="M6" t="n">
-        <v>11.18766422698198</v>
+        <v>11.17567496429119</v>
       </c>
       <c r="N6" t="n">
-        <v>188.6574967332944</v>
+        <v>188.8147466137444</v>
       </c>
       <c r="O6" t="n">
-        <v>13.73526471289485</v>
+        <v>13.74098783253025</v>
       </c>
       <c r="P6" t="n">
-        <v>355.7064042728277</v>
+        <v>355.5791577704114</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26199,28 +26320,28 @@
         <v>0.0849</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2914192940854912</v>
+        <v>-0.2812413179968219</v>
       </c>
       <c r="J7" t="n">
+        <v>208</v>
+      </c>
+      <c r="K7" t="n">
         <v>207</v>
       </c>
-      <c r="K7" t="n">
-        <v>206</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.03447775196203984</v>
+        <v>0.03234325730878096</v>
       </c>
       <c r="M7" t="n">
-        <v>9.968220662651987</v>
+        <v>9.951850267790673</v>
       </c>
       <c r="N7" t="n">
-        <v>153.3471349951478</v>
+        <v>153.3054250181871</v>
       </c>
       <c r="O7" t="n">
-        <v>12.38334102716822</v>
+        <v>12.38165679617179</v>
       </c>
       <c r="P7" t="n">
-        <v>368.6054480769217</v>
+        <v>368.502649792392</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26277,28 +26398,28 @@
         <v>0.0912</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3156285752512841</v>
+        <v>-0.3090275510563705</v>
       </c>
       <c r="J8" t="n">
+        <v>208</v>
+      </c>
+      <c r="K8" t="n">
         <v>207</v>
       </c>
-      <c r="K8" t="n">
-        <v>206</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.04903277842138409</v>
+        <v>0.0474223787271526</v>
       </c>
       <c r="M8" t="n">
-        <v>8.919580779026893</v>
+        <v>8.899419602100872</v>
       </c>
       <c r="N8" t="n">
-        <v>124.5797321248966</v>
+        <v>124.2719587228393</v>
       </c>
       <c r="O8" t="n">
-        <v>11.16152911230789</v>
+        <v>11.14773334462389</v>
       </c>
       <c r="P8" t="n">
-        <v>386.1868222323092</v>
+        <v>386.1201514170641</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26355,28 +26476,28 @@
         <v>0.0881</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2084506963652588</v>
+        <v>-0.1987909506275218</v>
       </c>
       <c r="J9" t="n">
+        <v>208</v>
+      </c>
+      <c r="K9" t="n">
         <v>207</v>
       </c>
-      <c r="K9" t="n">
-        <v>206</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.02431536079588426</v>
+        <v>0.02224835132436687</v>
       </c>
       <c r="M9" t="n">
-        <v>8.723291387531239</v>
+        <v>8.720913065081575</v>
       </c>
       <c r="N9" t="n">
-        <v>112.4219640765065</v>
+        <v>112.5085810055088</v>
       </c>
       <c r="O9" t="n">
-        <v>10.60292243093886</v>
+        <v>10.60700622256388</v>
       </c>
       <c r="P9" t="n">
-        <v>395.0146366733634</v>
+        <v>394.9170725523455</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26433,28 +26554,28 @@
         <v>0.0973</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1982650310739172</v>
+        <v>-0.1970019635433249</v>
       </c>
       <c r="J10" t="n">
+        <v>208</v>
+      </c>
+      <c r="K10" t="n">
         <v>207</v>
       </c>
-      <c r="K10" t="n">
-        <v>206</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.0258065914745943</v>
+        <v>0.02572272095713057</v>
       </c>
       <c r="M10" t="n">
-        <v>7.647090383378406</v>
+        <v>7.616224629999138</v>
       </c>
       <c r="N10" t="n">
-        <v>95.68029440477841</v>
+        <v>95.22883709807064</v>
       </c>
       <c r="O10" t="n">
-        <v>9.781630457381755</v>
+        <v>9.758526379432022</v>
       </c>
       <c r="P10" t="n">
-        <v>384.8874450703096</v>
+        <v>384.8746879981512</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26511,28 +26632,28 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2418073673999131</v>
+        <v>-0.2354708953465933</v>
       </c>
       <c r="J11" t="n">
+        <v>208</v>
+      </c>
+      <c r="K11" t="n">
         <v>207</v>
       </c>
-      <c r="K11" t="n">
-        <v>206</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.04377691823169472</v>
+        <v>0.04185692357555693</v>
       </c>
       <c r="M11" t="n">
-        <v>6.919604356855348</v>
+        <v>6.92609441750187</v>
       </c>
       <c r="N11" t="n">
-        <v>82.35098788349069</v>
+        <v>82.22411997044303</v>
       </c>
       <c r="O11" t="n">
-        <v>9.074744507890605</v>
+        <v>9.067751649137895</v>
       </c>
       <c r="P11" t="n">
-        <v>377.5593853241573</v>
+        <v>377.4953865044138</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26589,28 +26710,28 @@
         <v>0.0901</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2553646893841985</v>
+        <v>-0.2567529969888876</v>
       </c>
       <c r="J12" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K12" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05070594421608665</v>
+        <v>0.05168675236311182</v>
       </c>
       <c r="M12" t="n">
-        <v>6.832099583198041</v>
+        <v>6.806383989061109</v>
       </c>
       <c r="N12" t="n">
-        <v>79.67663577718194</v>
+        <v>79.30679397862833</v>
       </c>
       <c r="O12" t="n">
-        <v>8.926176996742891</v>
+        <v>8.905436203725696</v>
       </c>
       <c r="P12" t="n">
-        <v>370.6878203985112</v>
+        <v>370.7016961805798</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26667,28 +26788,28 @@
         <v>0.0857</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2543654891057436</v>
+        <v>-0.2572190468786359</v>
       </c>
       <c r="J13" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K13" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05379066974025648</v>
+        <v>0.05539423451618497</v>
       </c>
       <c r="M13" t="n">
-        <v>6.784050902001455</v>
+        <v>6.765817093002038</v>
       </c>
       <c r="N13" t="n">
-        <v>74.27866037439769</v>
+        <v>73.97739830913098</v>
       </c>
       <c r="O13" t="n">
-        <v>8.618506852952992</v>
+        <v>8.601011470119719</v>
       </c>
       <c r="P13" t="n">
-        <v>364.8483878475586</v>
+        <v>364.876908433085</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26745,28 +26866,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1610573307297424</v>
+        <v>-0.1670476095983543</v>
       </c>
       <c r="J14" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K14" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02713770424068596</v>
+        <v>0.02928853953294042</v>
       </c>
       <c r="M14" t="n">
-        <v>6.315826364334929</v>
+        <v>6.321623265022621</v>
       </c>
       <c r="N14" t="n">
-        <v>60.68853763794152</v>
+        <v>60.64287037554421</v>
       </c>
       <c r="O14" t="n">
-        <v>7.790284823929195</v>
+        <v>7.78735323300184</v>
       </c>
       <c r="P14" t="n">
-        <v>359.6847710557382</v>
+        <v>359.7446423723177</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -26823,28 +26944,28 @@
         <v>0.0984</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1747587161562813</v>
+        <v>-0.1814977501243566</v>
       </c>
       <c r="J15" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K15" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03045758361927131</v>
+        <v>0.03291936390951766</v>
       </c>
       <c r="M15" t="n">
-        <v>6.627259571329374</v>
+        <v>6.632847436803464</v>
       </c>
       <c r="N15" t="n">
-        <v>63.44778585438281</v>
+        <v>63.45422174660014</v>
       </c>
       <c r="O15" t="n">
-        <v>7.965411844618131</v>
+        <v>7.965815824295722</v>
       </c>
       <c r="P15" t="n">
-        <v>358.5698852495152</v>
+        <v>358.6372401832326</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -26901,28 +27022,28 @@
         <v>0.1072</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1625049989484188</v>
+        <v>-0.1712466976610473</v>
       </c>
       <c r="J16" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K16" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02990486582203111</v>
+        <v>0.03310387938526549</v>
       </c>
       <c r="M16" t="n">
-        <v>6.288856782456915</v>
+        <v>6.303612972073994</v>
       </c>
       <c r="N16" t="n">
-        <v>55.90791934303067</v>
+        <v>56.16323498107541</v>
       </c>
       <c r="O16" t="n">
-        <v>7.477159844689069</v>
+        <v>7.494213433114606</v>
       </c>
       <c r="P16" t="n">
-        <v>358.2767759607762</v>
+        <v>358.3641470202123</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -26979,28 +27100,28 @@
         <v>0.0876</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1884758604928046</v>
+        <v>-0.1970115955957575</v>
       </c>
       <c r="J17" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K17" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0390564911638811</v>
+        <v>0.04255094966676476</v>
       </c>
       <c r="M17" t="n">
-        <v>6.25517030548418</v>
+        <v>6.274337218582978</v>
       </c>
       <c r="N17" t="n">
-        <v>57.04052508901663</v>
+        <v>57.2659895805959</v>
       </c>
       <c r="O17" t="n">
-        <v>7.552517797994033</v>
+        <v>7.567429522671215</v>
       </c>
       <c r="P17" t="n">
-        <v>353.3272716290955</v>
+        <v>353.4125841345393</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -27057,28 +27178,28 @@
         <v>0.0929</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1111064414941298</v>
+        <v>-0.1209022739697953</v>
       </c>
       <c r="J18" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K18" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01477804836126129</v>
+        <v>0.01740467866978623</v>
       </c>
       <c r="M18" t="n">
-        <v>6.03250348414801</v>
+        <v>6.056003349122841</v>
       </c>
       <c r="N18" t="n">
-        <v>53.71095622809975</v>
+        <v>54.11085529104813</v>
       </c>
       <c r="O18" t="n">
-        <v>7.328775902434168</v>
+        <v>7.356008108413701</v>
       </c>
       <c r="P18" t="n">
-        <v>348.4152151284831</v>
+        <v>348.5131219872747</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -27135,28 +27256,28 @@
         <v>0.09810000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.04037311570948102</v>
+        <v>-0.05084234676300746</v>
       </c>
       <c r="J19" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K19" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L19" t="n">
-        <v>0.00154962752010035</v>
+        <v>0.002451736759323642</v>
       </c>
       <c r="M19" t="n">
-        <v>6.710370311640945</v>
+        <v>6.722685584810718</v>
       </c>
       <c r="N19" t="n">
-        <v>68.54110586451422</v>
+        <v>68.96329964042575</v>
       </c>
       <c r="O19" t="n">
-        <v>8.278955602279446</v>
+        <v>8.304414467042559</v>
       </c>
       <c r="P19" t="n">
-        <v>344.5573159389293</v>
+        <v>344.6619532455554</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -27213,28 +27334,28 @@
         <v>0.0948</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.07315122723952716</v>
+        <v>-0.08396673318064514</v>
       </c>
       <c r="J20" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K20" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L20" t="n">
-        <v>0.003769406607104231</v>
+        <v>0.004964535684934379</v>
       </c>
       <c r="M20" t="n">
-        <v>7.630593279026987</v>
+        <v>7.636389201747284</v>
       </c>
       <c r="N20" t="n">
-        <v>92.29911386745962</v>
+        <v>92.65763571685996</v>
       </c>
       <c r="O20" t="n">
-        <v>9.60724278174855</v>
+        <v>9.625883633041694</v>
       </c>
       <c r="P20" t="n">
-        <v>345.9010103985012</v>
+        <v>346.0091086347223</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -27291,28 +27412,28 @@
         <v>0.0984</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.06802847411382787</v>
+        <v>-0.07956384290786145</v>
       </c>
       <c r="J21" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K21" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L21" t="n">
-        <v>0.003346642028005054</v>
+        <v>0.004569337303213628</v>
       </c>
       <c r="M21" t="n">
-        <v>7.377596248504291</v>
+        <v>7.38482600004852</v>
       </c>
       <c r="N21" t="n">
-        <v>89.94639145457811</v>
+        <v>90.42657383861091</v>
       </c>
       <c r="O21" t="n">
-        <v>9.484007141212944</v>
+        <v>9.509288818760892</v>
       </c>
       <c r="P21" t="n">
-        <v>348.7164148827184</v>
+        <v>348.8317079654077</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -27369,28 +27490,28 @@
         <v>0.1042</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1244257710421866</v>
+        <v>-0.1363028103226039</v>
       </c>
       <c r="J22" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K22" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L22" t="n">
-        <v>0.00915615715539686</v>
+        <v>0.01097469442321863</v>
       </c>
       <c r="M22" t="n">
-        <v>7.657479774683116</v>
+        <v>7.672858194962513</v>
       </c>
       <c r="N22" t="n">
-        <v>109.3402517517406</v>
+        <v>109.7820573680157</v>
       </c>
       <c r="O22" t="n">
-        <v>10.45658891569046</v>
+        <v>10.47769332286528</v>
       </c>
       <c r="P22" t="n">
-        <v>354.5683538254578</v>
+        <v>354.6870618179208</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -27447,28 +27568,28 @@
         <v>0.09909999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1447323169652559</v>
+        <v>-0.1570746898568166</v>
       </c>
       <c r="J23" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K23" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L23" t="n">
-        <v>0.01131701399310925</v>
+        <v>0.0133127343526982</v>
       </c>
       <c r="M23" t="n">
-        <v>7.994071566592771</v>
+        <v>8.008438909761512</v>
       </c>
       <c r="N23" t="n">
-        <v>119.4328094247788</v>
+        <v>119.903388518327</v>
       </c>
       <c r="O23" t="n">
-        <v>10.92853189704723</v>
+        <v>10.95004057153794</v>
       </c>
       <c r="P23" t="n">
-        <v>361.1587648819808</v>
+        <v>361.2821237657561</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -27525,28 +27646,28 @@
         <v>0.1154</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1431857476963302</v>
+        <v>-0.1517193177380446</v>
       </c>
       <c r="J24" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K24" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L24" t="n">
-        <v>0.01004356113114979</v>
+        <v>0.01132634201558791</v>
       </c>
       <c r="M24" t="n">
-        <v>8.669154833077314</v>
+        <v>8.668542013659492</v>
       </c>
       <c r="N24" t="n">
-        <v>131.8849843779539</v>
+        <v>131.7503662770736</v>
       </c>
       <c r="O24" t="n">
-        <v>11.48411878978766</v>
+        <v>11.47825623851784</v>
       </c>
       <c r="P24" t="n">
-        <v>359.5125475494978</v>
+        <v>359.5978384157042</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -27603,28 +27724,28 @@
         <v>0.1198</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1032880278470045</v>
+        <v>-0.1146374661638711</v>
       </c>
       <c r="J25" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K25" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L25" t="n">
-        <v>0.005042423374898575</v>
+        <v>0.006223174454620395</v>
       </c>
       <c r="M25" t="n">
-        <v>8.861940442800433</v>
+        <v>8.869652736167074</v>
       </c>
       <c r="N25" t="n">
-        <v>137.3828868432141</v>
+        <v>137.6058265919175</v>
       </c>
       <c r="O25" t="n">
-        <v>11.72104461399299</v>
+        <v>11.73055099268221</v>
       </c>
       <c r="P25" t="n">
-        <v>353.9581171838976</v>
+        <v>354.0715519386684</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -27681,28 +27802,28 @@
         <v>0.1172</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.02594537306786901</v>
+        <v>-0.04080246039594259</v>
       </c>
       <c r="J26" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K26" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0002271160815064954</v>
+        <v>0.0005624509940055367</v>
       </c>
       <c r="M26" t="n">
-        <v>10.22469359048543</v>
+        <v>10.23944138491105</v>
       </c>
       <c r="N26" t="n">
-        <v>193.3929855417795</v>
+        <v>193.9770966890261</v>
       </c>
       <c r="O26" t="n">
-        <v>13.90658065599806</v>
+        <v>13.92756607196771</v>
       </c>
       <c r="P26" t="n">
-        <v>347.8445857120255</v>
+        <v>347.9930785281999</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -27759,28 +27880,28 @@
         <v>0.1254</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1278075302602791</v>
+        <v>0.1143948102421561</v>
       </c>
       <c r="J27" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K27" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L27" t="n">
-        <v>0.004486118201303957</v>
+        <v>0.003612548286946127</v>
       </c>
       <c r="M27" t="n">
-        <v>11.36546796113383</v>
+        <v>11.36983874309351</v>
       </c>
       <c r="N27" t="n">
-        <v>236.5684938272776</v>
+        <v>236.6649865481535</v>
       </c>
       <c r="O27" t="n">
-        <v>15.380783264427</v>
+        <v>15.38391973939521</v>
       </c>
       <c r="P27" t="n">
-        <v>343.7679322270538</v>
+        <v>343.9019889586373</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -27837,28 +27958,28 @@
         <v>0.1321</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2169392279365538</v>
+        <v>0.2042505051434667</v>
       </c>
       <c r="J28" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K28" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L28" t="n">
-        <v>0.01338894596102547</v>
+        <v>0.01194103124927248</v>
       </c>
       <c r="M28" t="n">
-        <v>11.55671974798087</v>
+        <v>11.55848526101675</v>
       </c>
       <c r="N28" t="n">
-        <v>226.3305507163184</v>
+        <v>226.3466577577139</v>
       </c>
       <c r="O28" t="n">
-        <v>15.04428631462186</v>
+        <v>15.04482162598527</v>
       </c>
       <c r="P28" t="n">
-        <v>343.0701145444484</v>
+        <v>343.196935107564</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -27915,28 +28036,28 @@
         <v>0.1514</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1805902227436562</v>
+        <v>0.1653712318003294</v>
       </c>
       <c r="J29" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K29" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L29" t="n">
-        <v>0.008374057651145961</v>
+        <v>0.007054004141505255</v>
       </c>
       <c r="M29" t="n">
-        <v>12.11368693676276</v>
+        <v>12.11816209643595</v>
       </c>
       <c r="N29" t="n">
-        <v>252.0390374275974</v>
+        <v>252.4158481010868</v>
       </c>
       <c r="O29" t="n">
-        <v>15.87573738216897</v>
+        <v>15.88760045132955</v>
       </c>
       <c r="P29" t="n">
-        <v>345.8595953106521</v>
+        <v>346.0117052615869</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -27993,28 +28114,28 @@
         <v>0.2</v>
       </c>
       <c r="I30" t="n">
-        <v>0.22314814702522</v>
+        <v>0.2083409314110593</v>
       </c>
       <c r="J30" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K30" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0126207051809395</v>
+        <v>0.01105838845816021</v>
       </c>
       <c r="M30" t="n">
-        <v>12.16226908169676</v>
+        <v>12.16227054647438</v>
       </c>
       <c r="N30" t="n">
-        <v>254.2461442473392</v>
+        <v>254.5275456841777</v>
       </c>
       <c r="O30" t="n">
-        <v>15.94509781241053</v>
+        <v>15.95391944583455</v>
       </c>
       <c r="P30" t="n">
-        <v>349.8669191464689</v>
+        <v>350.0149135075234</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -28071,28 +28192,28 @@
         <v>0.182</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1824456115201606</v>
+        <v>0.1653665412440258</v>
       </c>
       <c r="J31" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K31" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L31" t="n">
-        <v>0.008289290410943173</v>
+        <v>0.006832340377930568</v>
       </c>
       <c r="M31" t="n">
-        <v>12.09857434385709</v>
+        <v>12.101336083714</v>
       </c>
       <c r="N31" t="n">
-        <v>259.8973805960044</v>
+        <v>260.648445184684</v>
       </c>
       <c r="O31" t="n">
-        <v>16.1213330899155</v>
+        <v>16.14461040671728</v>
       </c>
       <c r="P31" t="n">
-        <v>349.3902501494542</v>
+        <v>349.5609511211146</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -28149,28 +28270,28 @@
         <v>0.166</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1727703021348048</v>
+        <v>0.1579086808873049</v>
       </c>
       <c r="J32" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K32" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L32" t="n">
-        <v>0.007101457312074011</v>
+        <v>0.005962539686500512</v>
       </c>
       <c r="M32" t="n">
-        <v>12.43118072035067</v>
+        <v>12.42536807825564</v>
       </c>
       <c r="N32" t="n">
-        <v>272.3723321263467</v>
+        <v>272.5776589985284</v>
       </c>
       <c r="O32" t="n">
-        <v>16.50370661779791</v>
+        <v>16.50992607489593</v>
       </c>
       <c r="P32" t="n">
-        <v>348.8376827848654</v>
+        <v>348.9862209164135</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -28227,28 +28348,28 @@
         <v>0.1505</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1629841982414933</v>
+        <v>0.1465616630447412</v>
       </c>
       <c r="J33" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K33" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L33" t="n">
-        <v>0.006333503290417153</v>
+        <v>0.005141491635329509</v>
       </c>
       <c r="M33" t="n">
-        <v>12.36461884607515</v>
+        <v>12.36703464754696</v>
       </c>
       <c r="N33" t="n">
-        <v>271.9913288241475</v>
+        <v>272.5333981081569</v>
       </c>
       <c r="O33" t="n">
-        <v>16.49215961674357</v>
+        <v>16.50858558775272</v>
       </c>
       <c r="P33" t="n">
-        <v>351.6250680174552</v>
+        <v>351.7892070876673</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -28305,28 +28426,28 @@
         <v>0.1493</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1006350523600416</v>
+        <v>0.08544119231484841</v>
       </c>
       <c r="J34" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K34" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L34" t="n">
-        <v>0.002296167880535549</v>
+        <v>0.001662832073575649</v>
       </c>
       <c r="M34" t="n">
-        <v>13.06872792520254</v>
+        <v>13.06069672795902</v>
       </c>
       <c r="N34" t="n">
-        <v>287.1864650197851</v>
+        <v>287.3890557521148</v>
       </c>
       <c r="O34" t="n">
-        <v>16.94657679355288</v>
+        <v>16.95255307474703</v>
       </c>
       <c r="P34" t="n">
-        <v>357.0933541634991</v>
+        <v>357.2452129374869</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -28364,7 +28485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI208"/>
+  <dimension ref="A1:AI209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65107,6 +65228,183 @@
         </is>
       </c>
     </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>-34.42600699635219,172.96361230619038</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>-34.42595144336026,172.96450962864583</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>-34.4259159983899,172.96540735365232</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>-34.42586062574828,172.96630467867396</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>-34.42579740828204,172.96720184571447</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-34.425684236390836,172.96809800948662</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>-34.42555809742249,172.9689801940014</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>-34.425332557775874,172.9697608060792</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>-34.4252043520872,172.97061454242908</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>-34.42491667893992,172.9714427943504</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>-34.42474373703805,172.97233437992438</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>-34.42449788632645,172.9731857209277</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>-34.424242521029655,172.97403181102706</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>-34.423953837404625,172.97486068494504</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>-34.42365470988731,172.97569403702494</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>-34.423324500207755,172.97651088123857</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>-34.422989517153574,172.9773134827481</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>-34.422642177993,172.97810751715045</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>-34.42227302166612,172.97888642324122</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>-34.42188783450826,172.9796542134041</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>-34.42148841504451,172.98041213466666</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>-34.421070648802896,172.98117418535642</t>
+        </is>
+      </c>
+      <c r="X209" t="inlineStr">
+        <is>
+          <t>-34.42059717895913,172.98188934062298</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>-34.42016516604877,172.98263264190325</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>-34.41973923145762,172.9833730321015</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>-34.4192444521627,172.98404211751134</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>-34.41874446944521,172.9847058161092</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>-34.41827069292799,172.98539666151976</t>
+        </is>
+      </c>
+      <c r="AD209" t="inlineStr">
+        <is>
+          <t>-34.41774197822485,172.98604945747823</t>
+        </is>
+      </c>
+      <c r="AE209" t="inlineStr">
+        <is>
+          <t>-34.41722441900619,172.98671590020592</t>
+        </is>
+      </c>
+      <c r="AF209" t="inlineStr">
+        <is>
+          <t>-34.416670406999444,172.98731589558298</t>
+        </is>
+      </c>
+      <c r="AG209" t="inlineStr">
+        <is>
+          <t>-34.41612494848677,172.9879240502705</t>
+        </is>
+      </c>
+      <c r="AH209" t="inlineStr">
+        <is>
+          <t>-34.415551185700295,172.98849560551585</t>
+        </is>
+      </c>
+      <c r="AI209" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
